--- a/data/options.xlsx
+++ b/data/options.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,6 +490,34 @@
       <c r="A9" t="inlineStr">
         <is>
           <t>其他</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>美团月付</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>测试支付</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>测试吃饭</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>测试中</t>
         </is>
       </c>
     </row>
@@ -504,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,6 +637,34 @@
       <c r="A15" t="inlineStr">
         <is>
           <t>其他</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>旅游</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>测试分类</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>测试不吃法</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>比测试</t>
         </is>
       </c>
     </row>
@@ -623,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,6 +717,20 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>09:00-17:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>12：00-19：12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
